--- a/data/mecon/precio-exportacion-crudo.xlsx
+++ b/data/mecon/precio-exportacion-crudo.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hlazarte\Documents\Seguimiento de mercado\Precios_Combustibles\Crudo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ministerio\Documents\2-archivos COMEX\Info_Trimestral\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11835"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6470"/>
   </bookViews>
   <sheets>
     <sheet name="precios" sheetId="1" r:id="rId1"/>
     <sheet name="tipos de crudo" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="39">
   <si>
     <t>TIPO DE CRUDO</t>
   </si>
@@ -135,23 +135,25 @@
     <t>*Precio FOB sin descuento de Derechos de Exportación</t>
   </si>
   <si>
-    <t>Precio FOB exportación (fuente Aduana)*</t>
-  </si>
-  <si>
     <t>Precios por tipo de crudo en dólares por barril. Promedios mensuales</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Precio FOB exportación (fuente SESCO)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="4">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]&quot;$&quot;\ \-#,##0"/>
-    <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="3">
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color indexed="24"/>
@@ -193,12 +195,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color indexed="24"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -541,9 +537,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -576,7 +572,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -588,82 +584,69 @@
     <xf numFmtId="17" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="6" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="7" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
@@ -953,25 +936,29 @@
     <tabColor rgb="FFFF0000"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AD25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Z42"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.53515625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.77734375" style="14" customWidth="1"/>
-    <col min="2" max="2" width="15.77734375" style="14" customWidth="1"/>
-    <col min="3" max="22" width="3.77734375" style="14" customWidth="1"/>
+    <col min="1" max="1" width="6.765625" style="14" customWidth="1"/>
+    <col min="2" max="2" width="15.765625" style="14" customWidth="1"/>
+    <col min="3" max="12" width="3.765625" style="14" customWidth="1"/>
+    <col min="13" max="13" width="4.23046875" style="14" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.61328125" style="14" bestFit="1" customWidth="1"/>
+    <col min="15" max="22" width="4.23046875" style="14" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="11.07421875"/>
     <col min="26" max="26" width="4" style="14" customWidth="1"/>
-    <col min="27" max="16384" width="11.5546875" style="14"/>
+    <col min="27" max="16384" width="11.53515625" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:26" ht="13" x14ac:dyDescent="0.35">
       <c r="A1" s="18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W1" s="14"/>
       <c r="X1" s="14"/>
       <c r="Y1" s="14"/>
     </row>
-    <row r="3" spans="1:26" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:26" ht="52.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="31" t="s">
         <v>34</v>
       </c>
@@ -979,7 +966,7 @@
         <v>30</v>
       </c>
       <c r="C3" s="38" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D3" s="39"/>
       <c r="E3" s="39"/>
@@ -1010,7 +997,7 @@
       <c r="X3" s="14"/>
       <c r="Y3" s="14"/>
     </row>
-    <row r="4" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="27" t="s">
         <v>29</v>
       </c>
@@ -1081,7 +1068,7 @@
       <c r="X4" s="14"/>
       <c r="Y4" s="14"/>
     </row>
-    <row r="5" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" ht="12.5" x14ac:dyDescent="0.35">
       <c r="A5" s="19">
         <v>43466</v>
       </c>
@@ -1089,16 +1076,22 @@
         <v>60.238993640699526</v>
       </c>
       <c r="C5" s="20">
-        <v>53.819322631666772</v>
-      </c>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
+        <v>56.30068210496691</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>37</v>
+      </c>
       <c r="F5" s="21">
-        <v>43.883298745567778</v>
-      </c>
-      <c r="G5" s="22"/>
+        <v>52.452913409479891</v>
+      </c>
+      <c r="G5" s="22" t="s">
+        <v>37</v>
+      </c>
       <c r="H5" s="20">
-        <v>50.308627207027101</v>
+        <v>50.300629015102295</v>
       </c>
       <c r="I5" s="21">
         <v>49.699218836607663</v>
@@ -1113,34 +1106,43 @@
         <v>50.666272550396648</v>
       </c>
       <c r="M5" s="21">
-        <f t="shared" ref="M5:M10" si="0">+C5-B5</f>
-        <v>-6.4196710090327542</v>
-      </c>
-      <c r="N5" s="21"/>
-      <c r="O5" s="21"/>
+        <f t="shared" ref="M5:M34" si="0">IF(C5="","",C5-$B5)</f>
+        <v>-3.9383115357326162</v>
+      </c>
+      <c r="N5" s="21" t="str">
+        <f t="shared" ref="N5:N34" si="1">IF(D5="","",D5-$B5)</f>
+        <v/>
+      </c>
+      <c r="O5" s="21" t="str">
+        <f t="shared" ref="O5:O34" si="2">IF(E5="","",E5-$B5)</f>
+        <v/>
+      </c>
       <c r="P5" s="21">
-        <f t="shared" ref="P5:P10" si="1">+F5-$B5</f>
-        <v>-16.355694895131748</v>
-      </c>
-      <c r="Q5" s="22"/>
-      <c r="R5" s="20">
-        <f t="shared" ref="R5:R10" si="2">+H5-$B5</f>
-        <v>-9.9303664336724253</v>
+        <f t="shared" ref="P5:P34" si="3">IF(F5="","",F5-$B5)</f>
+        <v>-7.7860802312196356</v>
+      </c>
+      <c r="Q5" s="22" t="str">
+        <f t="shared" ref="Q5:Q34" si="4">IF(G5="","",G5-$B5)</f>
+        <v/>
+      </c>
+      <c r="R5" s="21">
+        <f t="shared" ref="R5" si="5">IF(H5="","",H5-$B5)</f>
+        <v>-9.9383646255972309</v>
       </c>
       <c r="S5" s="21">
-        <f t="shared" ref="S5:S10" si="3">+I5-$B5</f>
+        <f t="shared" ref="S5" si="6">IF(I5="","",I5-$B5)</f>
         <v>-10.539774804091863</v>
       </c>
       <c r="T5" s="21">
-        <f t="shared" ref="T5:T10" si="4">+J5-$B5</f>
+        <f t="shared" ref="T5" si="7">IF(J5="","",J5-$B5)</f>
         <v>-6.2854507186170352</v>
       </c>
       <c r="U5" s="21">
-        <f t="shared" ref="U5:V10" si="5">+K5-$B5</f>
+        <f t="shared" ref="U5" si="8">IF(K5="","",K5-$B5)</f>
         <v>-12.982908015003879</v>
       </c>
       <c r="V5" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="V5" si="9">IF(L5="","",L5-$B5)</f>
         <v>-9.5727210903028777</v>
       </c>
       <c r="W5" s="34"/>
@@ -1148,7 +1150,7 @@
       <c r="Y5" s="14"/>
       <c r="Z5" s="17"/>
     </row>
-    <row r="6" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" ht="12.5" x14ac:dyDescent="0.35">
       <c r="A6" s="23">
         <v>43497</v>
       </c>
@@ -1156,20 +1158,22 @@
         <v>64.318481148021107</v>
       </c>
       <c r="C6" s="24">
-        <v>57.430926349731045</v>
-      </c>
-      <c r="D6" s="25"/>
+        <v>56.459474887738217</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>37</v>
+      </c>
       <c r="E6" s="25">
-        <v>55.162133247266148</v>
+        <v>57.194405305525123</v>
       </c>
       <c r="F6" s="25">
-        <v>47.340996768735657</v>
+        <v>48.736196684415901</v>
       </c>
       <c r="G6" s="26">
-        <v>56.762601373190854</v>
+        <v>59.208354046086363</v>
       </c>
       <c r="H6" s="24">
-        <v>53.265151547809069</v>
+        <v>53.256683320218002</v>
       </c>
       <c r="I6" s="25">
         <v>53.964349833126498</v>
@@ -1185,39 +1189,42 @@
       </c>
       <c r="M6" s="25">
         <f t="shared" si="0"/>
-        <v>-6.8875547982900613</v>
-      </c>
-      <c r="N6" s="25"/>
+        <v>-7.8590062602828894</v>
+      </c>
+      <c r="N6" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="O6" s="25">
-        <f>+E6-B6</f>
-        <v>-9.1563479007549589</v>
+        <f t="shared" si="2"/>
+        <v>-7.1240758424959836</v>
       </c>
       <c r="P6" s="25">
-        <f t="shared" si="1"/>
-        <v>-16.97748437928545</v>
+        <f t="shared" si="3"/>
+        <v>-15.582284463605205</v>
       </c>
       <c r="Q6" s="26">
-        <f>+G6-$B6</f>
-        <v>-7.5558797748302524</v>
+        <f t="shared" si="4"/>
+        <v>-5.1101271019347436</v>
       </c>
       <c r="R6" s="24">
-        <f t="shared" si="2"/>
-        <v>-11.053329600212038</v>
+        <f t="shared" ref="R6:R34" si="10">IF(H6="","",H6-$B6)</f>
+        <v>-11.061797827803105</v>
       </c>
       <c r="S6" s="25">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="S6:S34" si="11">IF(I6="","",I6-$B6)</f>
         <v>-10.354131314894609</v>
       </c>
       <c r="T6" s="25">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="T6:T34" si="12">IF(J6="","",J6-$B6)</f>
         <v>-11.752027478952513</v>
       </c>
       <c r="U6" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="U6:U34" si="13">IF(K6="","",K6-$B6)</f>
         <v>-21.807806635061972</v>
       </c>
       <c r="V6" s="26">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="V6:V34" si="14">IF(L6="","",L6-$B6)</f>
         <v>-10.539673131492876</v>
       </c>
       <c r="W6" s="34"/>
@@ -1225,7 +1232,7 @@
       <c r="Y6" s="14"/>
       <c r="Z6" s="17"/>
     </row>
-    <row r="7" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" ht="12.5" x14ac:dyDescent="0.35">
       <c r="A7" s="19">
         <v>43525</v>
       </c>
@@ -1233,18 +1240,22 @@
         <v>67.035011310470168</v>
       </c>
       <c r="C7" s="20">
-        <v>61.658019567512724</v>
-      </c>
-      <c r="D7" s="21"/>
+        <v>63.851098641717421</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>37</v>
+      </c>
       <c r="E7" s="21">
-        <v>55.129395942402802</v>
+        <v>57.062216340947565</v>
       </c>
       <c r="F7" s="21">
-        <v>55.637293738115581</v>
-      </c>
-      <c r="G7" s="22"/>
+        <v>58.420069530931649</v>
+      </c>
+      <c r="G7" s="22" t="s">
+        <v>37</v>
+      </c>
       <c r="H7" s="20">
-        <v>56.408596665431467</v>
+        <v>56.399628685039509</v>
       </c>
       <c r="I7" s="21">
         <v>57.644951567571695</v>
@@ -1260,43 +1271,49 @@
       </c>
       <c r="M7" s="21">
         <f t="shared" si="0"/>
-        <v>-5.3769917429574434</v>
-      </c>
-      <c r="N7" s="21"/>
+        <v>-3.1839126687527468</v>
+      </c>
+      <c r="N7" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="O7" s="21">
-        <f>+E7-$B7</f>
-        <v>-11.905615368067366</v>
+        <f t="shared" si="2"/>
+        <v>-9.972794969522603</v>
       </c>
       <c r="P7" s="21">
-        <f t="shared" si="1"/>
-        <v>-11.397717572354587</v>
-      </c>
-      <c r="Q7" s="22"/>
-      <c r="R7" s="20">
-        <f t="shared" si="2"/>
-        <v>-10.6264146450387</v>
+        <f t="shared" si="3"/>
+        <v>-8.614941779538519</v>
+      </c>
+      <c r="Q7" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="R7" s="21">
+        <f t="shared" si="10"/>
+        <v>-10.635382625430658</v>
       </c>
       <c r="S7" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>-9.3900597428984725</v>
       </c>
       <c r="T7" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>-13.39843007259951</v>
       </c>
       <c r="U7" s="21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>-14.258214729137684</v>
       </c>
       <c r="V7" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>-9.4484879166625575</v>
       </c>
       <c r="W7" s="34"/>
       <c r="X7" s="16"/>
       <c r="Y7" s="14"/>
     </row>
-    <row r="8" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" ht="12.5" x14ac:dyDescent="0.35">
       <c r="A8" s="23">
         <v>43556</v>
       </c>
@@ -1304,18 +1321,22 @@
         <v>71.628571428571433</v>
       </c>
       <c r="C8" s="24">
-        <v>64.614406106060216</v>
-      </c>
-      <c r="D8" s="25"/>
+        <v>68.846227630072931</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>37</v>
+      </c>
       <c r="E8" s="25">
-        <v>59.446898854057054</v>
+        <v>61.787945962676012</v>
       </c>
       <c r="F8" s="25">
-        <v>57.777254142812971</v>
-      </c>
-      <c r="G8" s="26"/>
+        <v>59.285092641658615</v>
+      </c>
+      <c r="G8" s="26" t="s">
+        <v>37</v>
+      </c>
       <c r="H8" s="24">
-        <v>60.923198392207276</v>
+        <v>60.913512669092455</v>
       </c>
       <c r="I8" s="25">
         <v>61.62963044742893</v>
@@ -1331,43 +1352,49 @@
       </c>
       <c r="M8" s="25">
         <f t="shared" si="0"/>
-        <v>-7.0141653225112179</v>
-      </c>
-      <c r="N8" s="25"/>
+        <v>-2.782343798498502</v>
+      </c>
+      <c r="N8" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="O8" s="25">
-        <f>+E8-$B8</f>
-        <v>-12.18167257451438</v>
+        <f t="shared" si="2"/>
+        <v>-9.8406254658954211</v>
       </c>
       <c r="P8" s="25">
-        <f t="shared" si="1"/>
-        <v>-13.851317285758462</v>
-      </c>
-      <c r="Q8" s="26"/>
+        <f t="shared" si="3"/>
+        <v>-12.343478786912819</v>
+      </c>
+      <c r="Q8" s="26" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="R8" s="24">
-        <f t="shared" si="2"/>
-        <v>-10.705373036364158</v>
+        <f t="shared" si="10"/>
+        <v>-10.715058759478978</v>
       </c>
       <c r="S8" s="25">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>-9.9989409811425034</v>
       </c>
       <c r="T8" s="25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>-13.371296822115717</v>
       </c>
       <c r="U8" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>-13.24105229993414</v>
       </c>
       <c r="V8" s="26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>-12.465649735370235</v>
       </c>
       <c r="W8" s="34"/>
       <c r="X8" s="16"/>
       <c r="Y8" s="14"/>
     </row>
-    <row r="9" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" ht="12.5" x14ac:dyDescent="0.35">
       <c r="A9" s="19">
         <v>43586</v>
       </c>
@@ -1375,16 +1402,22 @@
         <v>70.192380952380944</v>
       </c>
       <c r="C9" s="20">
-        <v>68.157250814490467</v>
-      </c>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
+        <v>67.921731360109291</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>37</v>
+      </c>
       <c r="F9" s="21">
-        <v>59.828101114429614</v>
-      </c>
-      <c r="G9" s="22"/>
+        <v>61.279718976592832</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>37</v>
+      </c>
       <c r="H9" s="20">
-        <v>64.6360794323504</v>
+        <v>64.625803426081347</v>
       </c>
       <c r="I9" s="21">
         <v>66.315473190416597</v>
@@ -1400,40 +1433,49 @@
       </c>
       <c r="M9" s="21">
         <f t="shared" si="0"/>
-        <v>-2.0351301378904765</v>
-      </c>
-      <c r="N9" s="21"/>
-      <c r="O9" s="21"/>
+        <v>-2.2706495922716528</v>
+      </c>
+      <c r="N9" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="O9" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="P9" s="21">
-        <f t="shared" si="1"/>
-        <v>-10.364279837951329</v>
-      </c>
-      <c r="Q9" s="22"/>
+        <f t="shared" si="3"/>
+        <v>-8.9126619757881116</v>
+      </c>
+      <c r="Q9" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="R9" s="20">
-        <f t="shared" si="2"/>
-        <v>-5.5563015200305443</v>
+        <f t="shared" si="10"/>
+        <v>-5.5665775262995965</v>
       </c>
       <c r="S9" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>-3.8769077619643468</v>
       </c>
       <c r="T9" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>-11.260231543279573</v>
       </c>
       <c r="U9" s="21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>-11.041323550568244</v>
       </c>
       <c r="V9" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>-8.2826014802770302</v>
       </c>
       <c r="W9" s="34"/>
       <c r="X9" s="16"/>
       <c r="Y9" s="14"/>
     </row>
-    <row r="10" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" ht="12.5" x14ac:dyDescent="0.35">
       <c r="A10" s="23">
         <v>43617</v>
       </c>
@@ -1441,20 +1483,22 @@
         <v>62.276666666666671</v>
       </c>
       <c r="C10" s="24">
-        <v>62.891984765312273</v>
-      </c>
-      <c r="D10" s="25"/>
+        <v>61.756402803121901</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>37</v>
+      </c>
       <c r="E10" s="25">
-        <v>54.564136724335846</v>
+        <v>55.150363633319202</v>
       </c>
       <c r="F10" s="25">
-        <v>52.109857775062629</v>
-      </c>
-      <c r="G10" s="26">
-        <v>53.501351545903191</v>
+        <v>51.500901092089563</v>
+      </c>
+      <c r="G10" s="26" t="s">
+        <v>37</v>
       </c>
       <c r="H10" s="24">
-        <v>58.699674853660738</v>
+        <v>58.6081571723971</v>
       </c>
       <c r="I10" s="25">
         <v>58.397833829498701</v>
@@ -1470,46 +1514,49 @@
       </c>
       <c r="M10" s="25">
         <f t="shared" si="0"/>
-        <v>0.61531809864560216</v>
-      </c>
-      <c r="N10" s="25"/>
+        <v>-0.52026386354476983</v>
+      </c>
+      <c r="N10" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="O10" s="25">
-        <f>+E10-$B10</f>
-        <v>-7.7125299423308249</v>
+        <f t="shared" si="2"/>
+        <v>-7.1263030333474688</v>
       </c>
       <c r="P10" s="25">
-        <f t="shared" si="1"/>
-        <v>-10.166808891604042</v>
-      </c>
-      <c r="Q10" s="26">
-        <f>+G10-$B10</f>
-        <v>-8.7753151207634801</v>
+        <f t="shared" si="3"/>
+        <v>-10.775765574577107</v>
+      </c>
+      <c r="Q10" s="26" t="str">
+        <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="R10" s="24">
-        <f t="shared" si="2"/>
-        <v>-3.5769918130059324</v>
+        <f t="shared" si="10"/>
+        <v>-3.6685094942695713</v>
       </c>
       <c r="S10" s="25">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>-3.8788328371679697</v>
       </c>
       <c r="T10" s="25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>-12.353805905838179</v>
       </c>
       <c r="U10" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>-11.781357396512433</v>
       </c>
       <c r="V10" s="26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>-4.5329554740950044</v>
       </c>
       <c r="W10" s="34"/>
       <c r="X10" s="16"/>
       <c r="Y10" s="14"/>
     </row>
-    <row r="11" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" ht="12.5" x14ac:dyDescent="0.35">
       <c r="A11" s="19">
         <v>43647</v>
       </c>
@@ -1517,18 +1564,22 @@
         <v>64.191818181818192</v>
       </c>
       <c r="C11" s="20">
-        <v>64.165892343535418</v>
-      </c>
-      <c r="D11" s="21"/>
+        <v>63.581545975339964</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>37</v>
+      </c>
       <c r="E11" s="21">
-        <v>55.20074787665969</v>
+        <v>54.757955571267907</v>
       </c>
       <c r="F11" s="21">
-        <v>52.604662673518291</v>
-      </c>
-      <c r="G11" s="22"/>
+        <v>55.321334642318369</v>
+      </c>
+      <c r="G11" s="22">
+        <v>52.807937855266502</v>
+      </c>
       <c r="H11" s="20">
-        <v>59.310045901219972</v>
+        <v>59.298359357615688</v>
       </c>
       <c r="I11" s="21">
         <v>60.949914942509317</v>
@@ -1543,44 +1594,50 @@
         <v>54.952252850965536</v>
       </c>
       <c r="M11" s="21">
-        <f t="shared" ref="M11:M13" si="6">+C11-B11</f>
-        <v>-2.5925838282773839E-2</v>
-      </c>
-      <c r="N11" s="21"/>
+        <f t="shared" si="0"/>
+        <v>-0.61027220647822844</v>
+      </c>
+      <c r="N11" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="O11" s="21">
-        <f>+E11-$B11</f>
-        <v>-8.9910703051585017</v>
+        <f t="shared" si="2"/>
+        <v>-9.4338626105502854</v>
       </c>
       <c r="P11" s="21">
-        <f t="shared" ref="P11:P13" si="7">+F11-$B11</f>
-        <v>-11.587155508299901</v>
-      </c>
-      <c r="Q11" s="22"/>
+        <f t="shared" si="3"/>
+        <v>-8.8704835394998227</v>
+      </c>
+      <c r="Q11" s="22">
+        <f t="shared" si="4"/>
+        <v>-11.38388032655169</v>
+      </c>
       <c r="R11" s="20">
-        <f t="shared" ref="R11:R12" si="8">+H11-$B11</f>
-        <v>-4.88177228059822</v>
+        <f t="shared" si="10"/>
+        <v>-4.8934588242025043</v>
       </c>
       <c r="S11" s="21">
-        <f t="shared" ref="S11:S12" si="9">+I11-$B11</f>
+        <f t="shared" si="11"/>
         <v>-3.2419032393088756</v>
       </c>
       <c r="T11" s="21">
-        <f t="shared" ref="T11:T12" si="10">+J11-$B11</f>
+        <f t="shared" si="12"/>
         <v>-14.314348217518621</v>
       </c>
       <c r="U11" s="21">
-        <f t="shared" ref="U11:U12" si="11">+K11-$B11</f>
+        <f t="shared" si="13"/>
         <v>-13.69650891166394</v>
       </c>
       <c r="V11" s="22">
-        <f t="shared" ref="V11:V12" si="12">+L11-$B11</f>
+        <f t="shared" si="14"/>
         <v>-9.2395653308526562</v>
       </c>
       <c r="W11" s="34"/>
       <c r="X11" s="16"/>
       <c r="Y11" s="14"/>
     </row>
-    <row r="12" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:26" ht="12.5" x14ac:dyDescent="0.35">
       <c r="A12" s="23">
         <v>43678</v>
       </c>
@@ -1588,18 +1645,22 @@
         <v>59.49</v>
       </c>
       <c r="C12" s="24">
-        <v>57.349338905266904</v>
-      </c>
-      <c r="D12" s="25"/>
+        <v>58.692226505429204</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>37</v>
+      </c>
       <c r="E12" s="25">
-        <v>50.685391180476834</v>
+        <v>51.996532618965688</v>
       </c>
       <c r="F12" s="25">
-        <v>45.892344114197357</v>
-      </c>
-      <c r="G12" s="26"/>
+        <v>51.841648573030696</v>
+      </c>
+      <c r="G12" s="26" t="s">
+        <v>37</v>
+      </c>
       <c r="H12" s="24">
-        <v>54.179366410462329</v>
+        <v>54.172987051812804</v>
       </c>
       <c r="I12" s="25">
         <v>55.042774364039502</v>
@@ -1614,44 +1675,50 @@
         <v>51.493429544348658</v>
       </c>
       <c r="M12" s="25">
-        <f t="shared" si="6"/>
-        <v>-2.1406610947330975</v>
-      </c>
-      <c r="N12" s="25"/>
+        <f t="shared" si="0"/>
+        <v>-0.79777349457079794</v>
+      </c>
+      <c r="N12" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="O12" s="25">
-        <f>+E12-$B12</f>
-        <v>-8.8046088195231675</v>
+        <f t="shared" si="2"/>
+        <v>-7.4934673810343142</v>
       </c>
       <c r="P12" s="25">
-        <f t="shared" si="7"/>
-        <v>-13.597655885802645</v>
-      </c>
-      <c r="Q12" s="26"/>
+        <f t="shared" si="3"/>
+        <v>-7.648351426969306</v>
+      </c>
+      <c r="Q12" s="26" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="R12" s="24">
-        <f t="shared" si="8"/>
-        <v>-5.3106335895376731</v>
+        <f t="shared" si="10"/>
+        <v>-5.3170129481871982</v>
       </c>
       <c r="S12" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-4.4472256359604998</v>
       </c>
       <c r="T12" s="25">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>-17.809720065612034</v>
       </c>
       <c r="U12" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-11.983882175226583</v>
       </c>
       <c r="V12" s="26">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-7.9965704556513444</v>
       </c>
       <c r="W12" s="34"/>
       <c r="X12" s="16"/>
       <c r="Y12" s="14"/>
     </row>
-    <row r="13" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" ht="12.5" x14ac:dyDescent="0.35">
       <c r="A13" s="19">
         <v>43709</v>
       </c>
@@ -1659,18 +1726,22 @@
         <v>62.29</v>
       </c>
       <c r="C13" s="20">
-        <v>58.576863840729743</v>
-      </c>
-      <c r="D13" s="21"/>
+        <v>61.859237739895924</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>37</v>
+      </c>
       <c r="E13" s="21">
-        <v>49.993480666063242</v>
+        <v>53.360844611001092</v>
       </c>
       <c r="F13" s="21">
-        <v>48.528187803522364</v>
-      </c>
-      <c r="G13" s="22"/>
+        <v>53.02912064056023</v>
+      </c>
+      <c r="G13" s="22" t="s">
+        <v>37</v>
+      </c>
       <c r="H13" s="20">
-        <v>49.792053282175594</v>
+        <v>49.78413721647096</v>
       </c>
       <c r="I13" s="21">
         <v>53.630122606182162</v>
@@ -1685,44 +1756,50 @@
         <v>49.723123234527705</v>
       </c>
       <c r="M13" s="21">
-        <f t="shared" si="6"/>
-        <v>-3.7131361592702561</v>
-      </c>
-      <c r="N13" s="21"/>
+        <f t="shared" si="0"/>
+        <v>-0.43076226010407481</v>
+      </c>
+      <c r="N13" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="O13" s="21">
-        <f>+E13-$B13</f>
-        <v>-12.296519333936757</v>
+        <f t="shared" si="2"/>
+        <v>-8.9291553889989075</v>
       </c>
       <c r="P13" s="21">
-        <f t="shared" si="7"/>
-        <v>-13.761812196477635</v>
-      </c>
-      <c r="Q13" s="22"/>
+        <f t="shared" si="3"/>
+        <v>-9.2608793594397696</v>
+      </c>
+      <c r="Q13" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="R13" s="20">
-        <f t="shared" ref="R13:R14" si="13">+H13-$B13</f>
-        <v>-12.497946717824405</v>
+        <f t="shared" si="10"/>
+        <v>-12.505862783529039</v>
       </c>
       <c r="S13" s="21">
-        <f t="shared" ref="S13:S14" si="14">+I13-$B13</f>
+        <f t="shared" si="11"/>
         <v>-8.6598773938178368</v>
       </c>
       <c r="T13" s="21">
-        <f t="shared" ref="T13:T14" si="15">+J13-$B13</f>
+        <f t="shared" si="12"/>
         <v>-14.304039268494193</v>
       </c>
       <c r="U13" s="21">
-        <f t="shared" ref="U13:U14" si="16">+K13-$B13</f>
+        <f t="shared" si="13"/>
         <v>-14.613860279853711</v>
       </c>
       <c r="V13" s="22">
-        <f t="shared" ref="V13:V14" si="17">+L13-$B13</f>
+        <f t="shared" si="14"/>
         <v>-12.566876765472294</v>
       </c>
       <c r="W13" s="14"/>
       <c r="X13" s="14"/>
       <c r="Y13" s="14"/>
     </row>
-    <row r="14" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:26" ht="12.5" x14ac:dyDescent="0.35">
       <c r="A14" s="23">
         <v>43739</v>
       </c>
@@ -1730,18 +1807,22 @@
         <v>59.632173913043466</v>
       </c>
       <c r="C14" s="24">
-        <v>62.158993171109366</v>
-      </c>
-      <c r="D14" s="25"/>
+        <v>60.84557436399313</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>37</v>
+      </c>
       <c r="E14" s="25">
-        <v>53.948110989609738</v>
+        <v>49.696649082930207</v>
       </c>
       <c r="F14" s="25">
-        <v>50.554595041447314</v>
-      </c>
-      <c r="G14" s="26"/>
+        <v>52.077524275486653</v>
+      </c>
+      <c r="G14" s="26" t="s">
+        <v>37</v>
+      </c>
       <c r="H14" s="24">
-        <v>47.756307927543382</v>
+        <v>47.748715509748855</v>
       </c>
       <c r="I14" s="25">
         <v>54.455243865319794</v>
@@ -1756,44 +1837,50 @@
         <v>49.56852670346278</v>
       </c>
       <c r="M14" s="25">
-        <f t="shared" ref="M14" si="18">+C14-B14</f>
-        <v>2.526819258065899</v>
-      </c>
-      <c r="N14" s="25"/>
+        <f t="shared" si="0"/>
+        <v>1.2134004509496634</v>
+      </c>
+      <c r="N14" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="O14" s="25">
-        <f>+E14-$B14</f>
-        <v>-5.6840629234337285</v>
+        <f t="shared" si="2"/>
+        <v>-9.935524830113259</v>
       </c>
       <c r="P14" s="25">
-        <f t="shared" ref="P14" si="19">+F14-$B14</f>
-        <v>-9.0775788715961525</v>
-      </c>
-      <c r="Q14" s="26"/>
+        <f t="shared" si="3"/>
+        <v>-7.554649637556814</v>
+      </c>
+      <c r="Q14" s="26" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="R14" s="24">
+        <f t="shared" si="10"/>
+        <v>-11.883458403294611</v>
+      </c>
+      <c r="S14" s="25">
+        <f t="shared" si="11"/>
+        <v>-5.1769300477236726</v>
+      </c>
+      <c r="T14" s="25">
+        <f t="shared" si="12"/>
+        <v>-18.478765849608934</v>
+      </c>
+      <c r="U14" s="25">
         <f t="shared" si="13"/>
-        <v>-11.875865985500084</v>
-      </c>
-      <c r="S14" s="25">
+        <v>-12.076049648454493</v>
+      </c>
+      <c r="V14" s="26">
         <f t="shared" si="14"/>
-        <v>-5.1769300477236726</v>
-      </c>
-      <c r="T14" s="25">
-        <f t="shared" si="15"/>
-        <v>-18.478765849608934</v>
-      </c>
-      <c r="U14" s="25">
-        <f t="shared" si="16"/>
-        <v>-12.076049648454493</v>
-      </c>
-      <c r="V14" s="26">
-        <f t="shared" si="17"/>
         <v>-10.063647209580687</v>
       </c>
       <c r="W14" s="34"/>
       <c r="X14" s="16"/>
       <c r="Y14" s="14"/>
     </row>
-    <row r="15" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" ht="12.5" x14ac:dyDescent="0.35">
       <c r="A15" s="19">
         <v>43770</v>
       </c>
@@ -1801,70 +1888,80 @@
         <v>62.65</v>
       </c>
       <c r="C15" s="20">
-        <v>60.679968789251873</v>
-      </c>
-      <c r="D15" s="21"/>
+        <v>62.108533476113415</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>37</v>
+      </c>
       <c r="E15" s="21">
-        <v>49.694815539957204</v>
+        <v>52.970436682805051</v>
       </c>
       <c r="F15" s="21">
-        <v>50.125973200909776</v>
-      </c>
-      <c r="G15" s="22"/>
+        <v>56.878898511105007</v>
+      </c>
+      <c r="G15" s="22" t="s">
+        <v>37</v>
+      </c>
       <c r="H15" s="20">
-        <v>54.021667055393422</v>
+        <v>54.121427709348147</v>
       </c>
       <c r="I15" s="21">
-        <v>53.171571017348477</v>
+        <v>53.58330865924561</v>
       </c>
       <c r="J15" s="21">
-        <v>51.84465386426556</v>
+        <v>51.844947262640275</v>
       </c>
       <c r="K15" s="21">
-        <v>50.381488498406107</v>
+        <v>50.381488114167603</v>
       </c>
       <c r="L15" s="22">
-        <v>49.452556986028988</v>
+        <v>49.61312901330767</v>
       </c>
       <c r="M15" s="21">
-        <f t="shared" ref="M15:M16" si="20">+C15-B15</f>
-        <v>-1.9700312107481253</v>
-      </c>
-      <c r="N15" s="21"/>
+        <f t="shared" si="0"/>
+        <v>-0.54146652388658367</v>
+      </c>
+      <c r="N15" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="O15" s="21">
-        <f t="shared" ref="O15" si="21">+E15-$B15</f>
-        <v>-12.955184460042794</v>
+        <f t="shared" si="2"/>
+        <v>-9.6795633171949476</v>
       </c>
       <c r="P15" s="21">
-        <f t="shared" ref="P15:P16" si="22">+F15-$B15</f>
-        <v>-12.524026799090223</v>
-      </c>
-      <c r="Q15" s="22"/>
+        <f t="shared" si="3"/>
+        <v>-5.7711014888949919</v>
+      </c>
+      <c r="Q15" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="R15" s="20">
-        <f t="shared" ref="R15:R16" si="23">+H15-$B15</f>
-        <v>-8.6283329446065764</v>
+        <f t="shared" si="10"/>
+        <v>-8.5285722906518515</v>
       </c>
       <c r="S15" s="21">
-        <f t="shared" ref="S15:S16" si="24">+I15-$B15</f>
-        <v>-9.478428982651522</v>
+        <f t="shared" si="11"/>
+        <v>-9.0666913407543888</v>
       </c>
       <c r="T15" s="21">
-        <f t="shared" ref="T15:T16" si="25">+J15-$B15</f>
-        <v>-10.805346135734439</v>
+        <f t="shared" si="12"/>
+        <v>-10.805052737359723</v>
       </c>
       <c r="U15" s="21">
-        <f t="shared" ref="U15:U16" si="26">+K15-$B15</f>
-        <v>-12.268511501593892</v>
+        <f t="shared" si="13"/>
+        <v>-12.268511885832396</v>
       </c>
       <c r="V15" s="22">
-        <f t="shared" ref="V15:V16" si="27">+L15-$B15</f>
-        <v>-13.197443013971011</v>
+        <f t="shared" si="14"/>
+        <v>-13.036870986692328</v>
       </c>
       <c r="W15" s="14"/>
       <c r="X15" s="14"/>
       <c r="Y15" s="14"/>
     </row>
-    <row r="16" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26" ht="12.5" x14ac:dyDescent="0.35">
       <c r="A16" s="23">
         <v>43800</v>
       </c>
@@ -1872,130 +1969,1551 @@
         <v>65.17</v>
       </c>
       <c r="C16" s="24">
-        <v>64.344092856292221</v>
-      </c>
-      <c r="D16" s="25"/>
+        <v>66.567506232011965</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>37</v>
+      </c>
       <c r="E16" s="25">
-        <v>50.765604817098755</v>
+        <v>55.19783248466711</v>
       </c>
       <c r="F16" s="25">
-        <v>52.438816905025853</v>
-      </c>
-      <c r="G16" s="26"/>
+        <v>55.080326985567858</v>
+      </c>
+      <c r="G16" s="26" t="s">
+        <v>37</v>
+      </c>
       <c r="H16" s="24">
-        <v>58.033676851475953</v>
+        <v>58.016292207679363</v>
       </c>
       <c r="I16" s="25">
-        <v>57.105004447699315</v>
+        <v>57.103802826788154</v>
       </c>
       <c r="J16" s="25">
         <v>49.649762759201835</v>
       </c>
       <c r="K16" s="25">
-        <v>50.381488114167603</v>
+        <v>52.896962951184605</v>
       </c>
       <c r="L16" s="26">
-        <v>52.071739535977706</v>
+        <v>52.020208049337953</v>
       </c>
       <c r="M16" s="25">
-        <f t="shared" si="20"/>
-        <v>-0.82590714370778073</v>
-      </c>
-      <c r="N16" s="25"/>
+        <f t="shared" si="0"/>
+        <v>1.3975062320119633</v>
+      </c>
+      <c r="N16" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="O16" s="25">
-        <f>+E16-$B16</f>
-        <v>-14.404395182901247</v>
+        <f t="shared" si="2"/>
+        <v>-9.9721675153328917</v>
       </c>
       <c r="P16" s="25">
-        <f t="shared" si="22"/>
-        <v>-12.731183094974149</v>
-      </c>
-      <c r="Q16" s="26"/>
+        <f t="shared" si="3"/>
+        <v>-10.089673014432144</v>
+      </c>
+      <c r="Q16" s="26" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="R16" s="24">
-        <f t="shared" si="23"/>
-        <v>-7.136323148524049</v>
+        <f t="shared" si="10"/>
+        <v>-7.1537077923206382</v>
       </c>
       <c r="S16" s="25">
-        <f t="shared" si="24"/>
-        <v>-8.0649955523006867</v>
+        <f t="shared" si="11"/>
+        <v>-8.0661971732118474</v>
       </c>
       <c r="T16" s="25">
-        <f t="shared" si="25"/>
+        <f t="shared" si="12"/>
         <v>-15.520237240798167</v>
       </c>
       <c r="U16" s="25">
-        <f t="shared" si="26"/>
-        <v>-14.788511885832399</v>
+        <f t="shared" si="13"/>
+        <v>-12.273037048815397</v>
       </c>
       <c r="V16" s="26">
-        <f t="shared" si="27"/>
-        <v>-13.098260464022296</v>
+        <f t="shared" si="14"/>
+        <v>-13.149791950662049</v>
       </c>
       <c r="W16" s="34"/>
       <c r="X16" s="16"/>
       <c r="Y16" s="14"/>
     </row>
-    <row r="17" spans="1:30" s="41" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="M17" s="42"/>
-      <c r="N17" s="42"/>
-      <c r="O17" s="42"/>
-      <c r="P17" s="42"/>
-      <c r="Q17" s="43"/>
-      <c r="Z17" s="44"/>
-      <c r="AB17" s="45"/>
-      <c r="AC17" s="45"/>
-      <c r="AD17" s="45"/>
-    </row>
-    <row r="18" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="W18" s="14"/>
-      <c r="X18" s="14"/>
+    <row r="17" spans="1:25" ht="12.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="19">
+        <v>43831</v>
+      </c>
+      <c r="B17" s="20">
+        <v>63.672727272727279</v>
+      </c>
+      <c r="C17" s="20">
+        <v>66.317332033705696</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17" s="21">
+        <v>49.827500436473919</v>
+      </c>
+      <c r="G17" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="H17" s="20">
+        <v>58.424810031007866</v>
+      </c>
+      <c r="I17" s="21">
+        <v>59.152644740036365</v>
+      </c>
+      <c r="J17" s="21">
+        <v>50.976625854666885</v>
+      </c>
+      <c r="K17" s="21">
+        <v>48.346167565242986</v>
+      </c>
+      <c r="L17" s="22">
+        <v>53.51264388065993</v>
+      </c>
+      <c r="M17" s="21">
+        <f t="shared" si="0"/>
+        <v>2.6446047609784173</v>
+      </c>
+      <c r="N17" s="21" t="str">
+        <f>IF(D17="","",D17-$B17)</f>
+        <v/>
+      </c>
+      <c r="O17" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="P17" s="21">
+        <f t="shared" si="3"/>
+        <v>-13.84522683625336</v>
+      </c>
+      <c r="Q17" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="R17" s="20">
+        <f t="shared" si="10"/>
+        <v>-5.2479172417194135</v>
+      </c>
+      <c r="S17" s="21">
+        <f t="shared" si="11"/>
+        <v>-4.520082532690914</v>
+      </c>
+      <c r="T17" s="21">
+        <f t="shared" si="12"/>
+        <v>-12.696101418060394</v>
+      </c>
+      <c r="U17" s="21">
+        <f t="shared" si="13"/>
+        <v>-15.326559707484293</v>
+      </c>
+      <c r="V17" s="22">
+        <f t="shared" si="14"/>
+        <v>-10.160083392067349</v>
+      </c>
+      <c r="W17" s="14"/>
+      <c r="X17" s="14"/>
+      <c r="Y17" s="14"/>
+    </row>
+    <row r="18" spans="1:25" ht="12.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="23">
+        <v>43862</v>
+      </c>
+      <c r="B18" s="24">
+        <v>55.477499999999999</v>
+      </c>
+      <c r="C18" s="24">
+        <v>56.247556004442671</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" s="25">
+        <v>45.964647589610685</v>
+      </c>
+      <c r="F18" s="25">
+        <v>38.151545106828792</v>
+      </c>
+      <c r="G18" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="H18" s="24">
+        <v>52.71392479982412</v>
+      </c>
+      <c r="I18" s="25">
+        <v>55.550124618737648</v>
+      </c>
+      <c r="J18" s="25">
+        <v>44.943234218476711</v>
+      </c>
+      <c r="K18" s="25"/>
+      <c r="L18" s="26">
+        <v>50.555118701652773</v>
+      </c>
+      <c r="M18" s="25">
+        <f t="shared" si="0"/>
+        <v>0.7700560044426723</v>
+      </c>
+      <c r="N18" s="25" t="str">
+        <f t="shared" ref="N18:N34" si="15">IF(D18="","",D18-$B18)</f>
+        <v/>
+      </c>
+      <c r="O18" s="25">
+        <f t="shared" si="2"/>
+        <v>-9.5128524103893142</v>
+      </c>
+      <c r="P18" s="25">
+        <f t="shared" si="3"/>
+        <v>-17.325954893171208</v>
+      </c>
+      <c r="Q18" s="26" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="R18" s="24">
+        <f t="shared" si="10"/>
+        <v>-2.7635752001758789</v>
+      </c>
+      <c r="S18" s="25">
+        <f t="shared" si="11"/>
+        <v>7.2624618737648916E-2</v>
+      </c>
+      <c r="T18" s="25">
+        <f t="shared" si="12"/>
+        <v>-10.534265781523288</v>
+      </c>
+      <c r="U18" s="25" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="V18" s="26">
+        <f t="shared" si="14"/>
+        <v>-4.9223812983472257</v>
+      </c>
+      <c r="W18" s="34"/>
+      <c r="X18" s="16"/>
       <c r="Y18" s="14"/>
-      <c r="Z18" s="15"/>
-    </row>
-    <row r="19" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A19" s="33" t="s">
-        <v>35</v>
+    </row>
+    <row r="19" spans="1:25" ht="12.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="19">
+        <v>43891</v>
+      </c>
+      <c r="B19" s="20">
+        <v>32.979999999999997</v>
+      </c>
+      <c r="C19" s="20">
+        <v>33.578569338126535</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" s="21">
+        <v>21.508142597489229</v>
+      </c>
+      <c r="F19" s="21">
+        <v>26.233332927624915</v>
+      </c>
+      <c r="G19" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="H19" s="20">
+        <v>48.107992733128818</v>
+      </c>
+      <c r="I19" s="21">
+        <v>48.464968460863929</v>
+      </c>
+      <c r="J19" s="21">
+        <v>24.80044522181587</v>
+      </c>
+      <c r="K19" s="21"/>
+      <c r="L19" s="22">
+        <v>41.650358282457219</v>
+      </c>
+      <c r="M19" s="21">
+        <f t="shared" si="0"/>
+        <v>0.59856933812653779</v>
+      </c>
+      <c r="N19" s="21" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="O19" s="21">
+        <f t="shared" si="2"/>
+        <v>-11.471857402510768</v>
+      </c>
+      <c r="P19" s="21">
+        <f t="shared" si="3"/>
+        <v>-6.7466670723750823</v>
+      </c>
+      <c r="Q19" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="R19" s="20">
+        <f t="shared" si="10"/>
+        <v>15.127992733128821</v>
+      </c>
+      <c r="S19" s="21">
+        <f t="shared" si="11"/>
+        <v>15.484968460863932</v>
+      </c>
+      <c r="T19" s="21">
+        <f t="shared" si="12"/>
+        <v>-8.1795547781841265</v>
+      </c>
+      <c r="U19" s="21" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="V19" s="22">
+        <f t="shared" si="14"/>
+        <v>8.6703582824572223</v>
       </c>
       <c r="W19" s="14"/>
       <c r="X19" s="14"/>
       <c r="Y19" s="14"/>
-      <c r="Z19" s="15"/>
-    </row>
-    <row r="20" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="W20" s="14"/>
-      <c r="X20" s="14"/>
+    </row>
+    <row r="20" spans="1:25" ht="12.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="23">
+        <v>43922</v>
+      </c>
+      <c r="B20" s="24">
+        <v>26.63</v>
+      </c>
+      <c r="C20" s="24">
+        <v>23.705880066293883</v>
+      </c>
+      <c r="D20" s="25">
+        <v>10.14385827657696</v>
+      </c>
+      <c r="E20" s="25">
+        <v>15.632012959657006</v>
+      </c>
+      <c r="F20" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="G20" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="H20" s="24">
+        <v>24.975348164040692</v>
+      </c>
+      <c r="I20" s="25">
+        <v>19.747869590124033</v>
+      </c>
+      <c r="J20" s="25"/>
+      <c r="K20" s="25"/>
+      <c r="L20" s="26">
+        <v>23.310703600929333</v>
+      </c>
+      <c r="M20" s="25">
+        <f t="shared" si="0"/>
+        <v>-2.9241199337061161</v>
+      </c>
+      <c r="N20" s="25">
+        <f t="shared" si="15"/>
+        <v>-16.486141723423039</v>
+      </c>
+      <c r="O20" s="25">
+        <f t="shared" si="2"/>
+        <v>-10.997987040342993</v>
+      </c>
+      <c r="P20" s="25" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="Q20" s="26" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="R20" s="24">
+        <f t="shared" si="10"/>
+        <v>-1.6546518359593065</v>
+      </c>
+      <c r="S20" s="25">
+        <f t="shared" si="11"/>
+        <v>-6.8821304098759661</v>
+      </c>
+      <c r="T20" s="25" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="U20" s="25" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="V20" s="26">
+        <f t="shared" si="14"/>
+        <v>-3.3192963990706659</v>
+      </c>
+      <c r="W20" s="34"/>
+      <c r="X20" s="16"/>
       <c r="Y20" s="14"/>
-      <c r="Z20" s="15"/>
-    </row>
-    <row r="21" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:25" ht="12.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="19">
+        <v>43952</v>
+      </c>
+      <c r="B21" s="20">
+        <v>32.26</v>
+      </c>
+      <c r="C21" s="20">
+        <v>20.902591684001322</v>
+      </c>
+      <c r="D21" s="21">
+        <v>24.004497272435454</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="F21" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="G21" s="22">
+        <v>24.094136097543899</v>
+      </c>
+      <c r="H21" s="20">
+        <v>26.167294948187287</v>
+      </c>
+      <c r="I21" s="21">
+        <v>32.791855710712227</v>
+      </c>
+      <c r="J21" s="21"/>
+      <c r="K21" s="21"/>
+      <c r="L21" s="22">
+        <v>29.007613335771048</v>
+      </c>
+      <c r="M21" s="21">
+        <f t="shared" si="0"/>
+        <v>-11.357408315998676</v>
+      </c>
+      <c r="N21" s="21">
+        <f t="shared" si="15"/>
+        <v>-8.2555027275645436</v>
+      </c>
+      <c r="O21" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="P21" s="21" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="Q21" s="22">
+        <f t="shared" si="4"/>
+        <v>-8.1658639024560991</v>
+      </c>
+      <c r="R21" s="20">
+        <f t="shared" si="10"/>
+        <v>-6.092705051812711</v>
+      </c>
+      <c r="S21" s="21">
+        <f t="shared" si="11"/>
+        <v>0.53185571071222881</v>
+      </c>
+      <c r="T21" s="21" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="U21" s="21" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="V21" s="22">
+        <f t="shared" si="14"/>
+        <v>-3.2523866642289505</v>
+      </c>
       <c r="W21" s="14"/>
       <c r="X21" s="14"/>
       <c r="Y21" s="14"/>
-      <c r="Z21" s="15"/>
-    </row>
-    <row r="22" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="W22" s="14"/>
-      <c r="X22" s="14"/>
+    </row>
+    <row r="22" spans="1:25" ht="12.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="23">
+        <v>43983</v>
+      </c>
+      <c r="B22" s="24">
+        <v>40.770000000000003</v>
+      </c>
+      <c r="C22" s="24">
+        <v>30.031511457832163</v>
+      </c>
+      <c r="D22" s="25">
+        <v>36.792153879865104</v>
+      </c>
+      <c r="E22" s="25">
+        <v>16.002062718052095</v>
+      </c>
+      <c r="F22" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="G22" s="26">
+        <v>27.59845524011974</v>
+      </c>
+      <c r="H22" s="24">
+        <v>39.760947889996302</v>
+      </c>
+      <c r="I22" s="25">
+        <v>40.377481665320701</v>
+      </c>
+      <c r="J22" s="25"/>
+      <c r="K22" s="25">
+        <v>18.756400063603117</v>
+      </c>
+      <c r="L22" s="26">
+        <v>42.333661080620359</v>
+      </c>
+      <c r="M22" s="25">
+        <f t="shared" si="0"/>
+        <v>-10.73848854216784</v>
+      </c>
+      <c r="N22" s="25">
+        <f t="shared" si="15"/>
+        <v>-3.9778461201348989</v>
+      </c>
+      <c r="O22" s="25">
+        <f t="shared" si="2"/>
+        <v>-24.767937281947908</v>
+      </c>
+      <c r="P22" s="25" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="Q22" s="26">
+        <f t="shared" si="4"/>
+        <v>-13.171544759880263</v>
+      </c>
+      <c r="R22" s="24">
+        <f t="shared" si="10"/>
+        <v>-1.0090521100037009</v>
+      </c>
+      <c r="S22" s="25">
+        <f t="shared" si="11"/>
+        <v>-0.39251833467930197</v>
+      </c>
+      <c r="T22" s="25" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="U22" s="25">
+        <f t="shared" si="13"/>
+        <v>-22.013599936396886</v>
+      </c>
+      <c r="V22" s="26">
+        <f t="shared" si="14"/>
+        <v>1.5636610806203564</v>
+      </c>
+      <c r="W22" s="34"/>
+      <c r="X22" s="16"/>
       <c r="Y22" s="14"/>
-      <c r="Z22" s="15"/>
-    </row>
-    <row r="23" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:25" ht="12.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="19">
+        <v>44013</v>
+      </c>
+      <c r="B23" s="20">
+        <v>43.22</v>
+      </c>
+      <c r="C23" s="20">
+        <v>28.815117967135436</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E23" s="21">
+        <v>30.660952823027554</v>
+      </c>
+      <c r="F23" s="21">
+        <v>31.668038979624292</v>
+      </c>
+      <c r="G23" s="22">
+        <v>37.090666744616435</v>
+      </c>
+      <c r="H23" s="20">
+        <v>41.086503594611962</v>
+      </c>
+      <c r="I23" s="21">
+        <v>40.630057438956939</v>
+      </c>
+      <c r="J23" s="21">
+        <v>16</v>
+      </c>
+      <c r="K23" s="21"/>
+      <c r="L23" s="22">
+        <v>43.049365582442427</v>
+      </c>
+      <c r="M23" s="21">
+        <f t="shared" si="0"/>
+        <v>-14.404882032864563</v>
+      </c>
+      <c r="N23" s="21" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="O23" s="21">
+        <f t="shared" si="2"/>
+        <v>-12.559047176972445</v>
+      </c>
+      <c r="P23" s="21">
+        <f t="shared" si="3"/>
+        <v>-11.551961020375707</v>
+      </c>
+      <c r="Q23" s="22">
+        <f t="shared" si="4"/>
+        <v>-6.129333255383564</v>
+      </c>
+      <c r="R23" s="20">
+        <f t="shared" si="10"/>
+        <v>-2.133496405388037</v>
+      </c>
+      <c r="S23" s="21">
+        <f t="shared" si="11"/>
+        <v>-2.5899425610430598</v>
+      </c>
+      <c r="T23" s="21">
+        <f t="shared" si="12"/>
+        <v>-27.22</v>
+      </c>
+      <c r="U23" s="21" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="V23" s="22">
+        <f t="shared" si="14"/>
+        <v>-0.17063441755757225</v>
+      </c>
       <c r="W23" s="14"/>
       <c r="X23" s="14"/>
       <c r="Y23" s="14"/>
-      <c r="Z23" s="15"/>
-    </row>
-    <row r="24" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="W24" s="14"/>
-      <c r="X24" s="14"/>
+    </row>
+    <row r="24" spans="1:25" ht="12.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="23">
+        <v>44044</v>
+      </c>
+      <c r="B24" s="24">
+        <v>45.02</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" s="25">
+        <v>28.13206260476424</v>
+      </c>
+      <c r="F24" s="25">
+        <v>28.254517240304335</v>
+      </c>
+      <c r="G24" s="26">
+        <v>41.042545020960247</v>
+      </c>
+      <c r="H24" s="24">
+        <v>41.245563378374591</v>
+      </c>
+      <c r="I24" s="25">
+        <v>41.577800870491664</v>
+      </c>
+      <c r="J24" s="25">
+        <v>19</v>
+      </c>
+      <c r="K24" s="25"/>
+      <c r="L24" s="26">
+        <v>43.521439102103002</v>
+      </c>
+      <c r="M24" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N24" s="25" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="O24" s="25">
+        <f t="shared" si="2"/>
+        <v>-16.887937395235763</v>
+      </c>
+      <c r="P24" s="25">
+        <f t="shared" si="3"/>
+        <v>-16.765482759695669</v>
+      </c>
+      <c r="Q24" s="26">
+        <f t="shared" si="4"/>
+        <v>-3.9774549790397558</v>
+      </c>
+      <c r="R24" s="24">
+        <f t="shared" si="10"/>
+        <v>-3.7744366216254122</v>
+      </c>
+      <c r="S24" s="25">
+        <f t="shared" si="11"/>
+        <v>-3.4421991295083387</v>
+      </c>
+      <c r="T24" s="25">
+        <f t="shared" si="12"/>
+        <v>-26.020000000000003</v>
+      </c>
+      <c r="U24" s="25" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="V24" s="26">
+        <f t="shared" si="14"/>
+        <v>-1.4985608978970006</v>
+      </c>
+      <c r="W24" s="34"/>
+      <c r="X24" s="16"/>
       <c r="Y24" s="14"/>
-      <c r="Z24" s="15"/>
-    </row>
-    <row r="25" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:25" ht="12.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="19">
+        <v>44075</v>
+      </c>
+      <c r="B25" s="20">
+        <v>41.87</v>
+      </c>
+      <c r="C25" s="20">
+        <v>40.607373836193034</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E25" s="21">
+        <v>34.754477049609861</v>
+      </c>
+      <c r="F25" s="21">
+        <v>28.98106353497036</v>
+      </c>
+      <c r="G25" s="22">
+        <v>40.940543642593084</v>
+      </c>
+      <c r="H25" s="20">
+        <v>42.983675253650148</v>
+      </c>
+      <c r="I25" s="21">
+        <v>44.125084386493519</v>
+      </c>
+      <c r="J25" s="21">
+        <v>19.000000000000004</v>
+      </c>
+      <c r="K25" s="21"/>
+      <c r="L25" s="22">
+        <v>39.86394437551116</v>
+      </c>
+      <c r="M25" s="21">
+        <f t="shared" si="0"/>
+        <v>-1.2626261638069636</v>
+      </c>
+      <c r="N25" s="21" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="O25" s="21">
+        <f t="shared" si="2"/>
+        <v>-7.1155229503901367</v>
+      </c>
+      <c r="P25" s="21">
+        <f t="shared" si="3"/>
+        <v>-12.888936465029637</v>
+      </c>
+      <c r="Q25" s="22">
+        <f t="shared" si="4"/>
+        <v>-0.92945635740691301</v>
+      </c>
+      <c r="R25" s="20">
+        <f t="shared" si="10"/>
+        <v>1.1136752536501504</v>
+      </c>
+      <c r="S25" s="21">
+        <f t="shared" si="11"/>
+        <v>2.2550843864935217</v>
+      </c>
+      <c r="T25" s="21">
+        <f t="shared" si="12"/>
+        <v>-22.869999999999994</v>
+      </c>
+      <c r="U25" s="21" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="V25" s="22">
+        <f t="shared" si="14"/>
+        <v>-2.0060556244888375</v>
+      </c>
       <c r="W25" s="14"/>
       <c r="X25" s="14"/>
       <c r="Y25" s="14"/>
-      <c r="Z25" s="15"/>
+    </row>
+    <row r="26" spans="1:25" ht="12.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="23">
+        <v>44105</v>
+      </c>
+      <c r="B26" s="24">
+        <v>41.42</v>
+      </c>
+      <c r="C26" s="24">
+        <v>39.153470878000618</v>
+      </c>
+      <c r="D26" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="E26" s="25">
+        <v>34.552454276991519</v>
+      </c>
+      <c r="F26" s="25">
+        <v>28.547696019626624</v>
+      </c>
+      <c r="G26" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="H26" s="24">
+        <v>42.021584591985054</v>
+      </c>
+      <c r="I26" s="25">
+        <v>42.908718417877736</v>
+      </c>
+      <c r="J26" s="25">
+        <v>23</v>
+      </c>
+      <c r="K26" s="25"/>
+      <c r="L26" s="26">
+        <v>38.683116320171408</v>
+      </c>
+      <c r="M26" s="25">
+        <f t="shared" si="0"/>
+        <v>-2.2665291219993833</v>
+      </c>
+      <c r="N26" s="25" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="O26" s="25">
+        <f t="shared" si="2"/>
+        <v>-6.8675457230084831</v>
+      </c>
+      <c r="P26" s="25">
+        <f t="shared" si="3"/>
+        <v>-12.872303980373378</v>
+      </c>
+      <c r="Q26" s="26" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="R26" s="24">
+        <f t="shared" si="10"/>
+        <v>0.60158459198505199</v>
+      </c>
+      <c r="S26" s="25">
+        <f t="shared" si="11"/>
+        <v>1.4887184178777346</v>
+      </c>
+      <c r="T26" s="25">
+        <f t="shared" si="12"/>
+        <v>-18.420000000000002</v>
+      </c>
+      <c r="U26" s="25" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="V26" s="26">
+        <f t="shared" si="14"/>
+        <v>-2.736883679828594</v>
+      </c>
+      <c r="W26" s="34"/>
+      <c r="X26" s="16"/>
+      <c r="Y26" s="14"/>
+    </row>
+    <row r="27" spans="1:25" ht="12.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="19">
+        <v>44136</v>
+      </c>
+      <c r="B27" s="20">
+        <v>43.6</v>
+      </c>
+      <c r="C27" s="20">
+        <v>43.685371877708953</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E27" s="21">
+        <v>38.218916105677884</v>
+      </c>
+      <c r="F27" s="21">
+        <v>31.817933568498997</v>
+      </c>
+      <c r="G27" s="22">
+        <v>39.846128416282369</v>
+      </c>
+      <c r="H27" s="20">
+        <v>43.41412349483948</v>
+      </c>
+      <c r="I27" s="21">
+        <v>42.774388425737378</v>
+      </c>
+      <c r="J27" s="21">
+        <v>26.396758659857337</v>
+      </c>
+      <c r="K27" s="21"/>
+      <c r="L27" s="22">
+        <v>38.811680852590825</v>
+      </c>
+      <c r="M27" s="21">
+        <f t="shared" si="0"/>
+        <v>8.537187770895116E-2</v>
+      </c>
+      <c r="N27" s="21" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="O27" s="21">
+        <f t="shared" si="2"/>
+        <v>-5.3810838943221171</v>
+      </c>
+      <c r="P27" s="21">
+        <f t="shared" si="3"/>
+        <v>-11.782066431501004</v>
+      </c>
+      <c r="Q27" s="22">
+        <f t="shared" si="4"/>
+        <v>-3.7538715837176326</v>
+      </c>
+      <c r="R27" s="20">
+        <f t="shared" si="10"/>
+        <v>-0.18587650516052179</v>
+      </c>
+      <c r="S27" s="21">
+        <f t="shared" si="11"/>
+        <v>-0.82561157426262355</v>
+      </c>
+      <c r="T27" s="21">
+        <f t="shared" si="12"/>
+        <v>-17.203241340142664</v>
+      </c>
+      <c r="U27" s="21" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="V27" s="22">
+        <f t="shared" si="14"/>
+        <v>-4.788319147409176</v>
+      </c>
+      <c r="W27" s="14"/>
+      <c r="X27" s="14"/>
+      <c r="Y27" s="14"/>
+    </row>
+    <row r="28" spans="1:25" ht="12.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="23">
+        <v>44166</v>
+      </c>
+      <c r="B28" s="24">
+        <v>50.22</v>
+      </c>
+      <c r="C28" s="24">
+        <v>49.745985773679649</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="E28" s="25">
+        <v>43.909659711817206</v>
+      </c>
+      <c r="F28" s="25">
+        <v>42.891052828117893</v>
+      </c>
+      <c r="G28" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="H28" s="24">
+        <v>49.302959493071072</v>
+      </c>
+      <c r="I28" s="25">
+        <v>48.538836010099018</v>
+      </c>
+      <c r="J28" s="25">
+        <v>30.675447408265278</v>
+      </c>
+      <c r="K28" s="25"/>
+      <c r="L28" s="26">
+        <v>43.425179128328701</v>
+      </c>
+      <c r="M28" s="25">
+        <f t="shared" si="0"/>
+        <v>-0.47401422632034951</v>
+      </c>
+      <c r="N28" s="25" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="O28" s="25">
+        <f t="shared" si="2"/>
+        <v>-6.3103402881827932</v>
+      </c>
+      <c r="P28" s="25">
+        <f t="shared" si="3"/>
+        <v>-7.3289471718821062</v>
+      </c>
+      <c r="Q28" s="26" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="R28" s="24">
+        <f t="shared" si="10"/>
+        <v>-0.91704050692892736</v>
+      </c>
+      <c r="S28" s="25">
+        <f t="shared" si="11"/>
+        <v>-1.6811639899009805</v>
+      </c>
+      <c r="T28" s="25">
+        <f t="shared" si="12"/>
+        <v>-19.544552591734721</v>
+      </c>
+      <c r="U28" s="25" t="str">
+        <f>IF(K28="","",K28-$B28)</f>
+        <v/>
+      </c>
+      <c r="V28" s="26">
+        <f t="shared" si="14"/>
+        <v>-6.7948208716712983</v>
+      </c>
+      <c r="W28" s="34"/>
+      <c r="X28" s="16"/>
+      <c r="Y28" s="14"/>
+    </row>
+    <row r="29" spans="1:25" ht="12.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="19">
+        <v>44197</v>
+      </c>
+      <c r="B29" s="20">
+        <v>55.32</v>
+      </c>
+      <c r="C29" s="20">
+        <v>56.849506443917925</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E29" s="21">
+        <v>49.954451480163918</v>
+      </c>
+      <c r="F29" s="21">
+        <v>41.047453334498591</v>
+      </c>
+      <c r="G29" s="22">
+        <v>47.118850653589483</v>
+      </c>
+      <c r="H29" s="20">
+        <v>53.703465898459264</v>
+      </c>
+      <c r="I29" s="21">
+        <v>53.264149373568955</v>
+      </c>
+      <c r="J29" s="21">
+        <v>30.050000000000004</v>
+      </c>
+      <c r="K29" s="21"/>
+      <c r="L29" s="22">
+        <v>47.966230318015548</v>
+      </c>
+      <c r="M29" s="21">
+        <f t="shared" si="0"/>
+        <v>1.5295064439179242</v>
+      </c>
+      <c r="N29" s="21" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="O29" s="21">
+        <f t="shared" si="2"/>
+        <v>-5.3655485198360822</v>
+      </c>
+      <c r="P29" s="21">
+        <f t="shared" si="3"/>
+        <v>-14.272546665501409</v>
+      </c>
+      <c r="Q29" s="22">
+        <f t="shared" si="4"/>
+        <v>-8.2011493464105172</v>
+      </c>
+      <c r="R29" s="20">
+        <f t="shared" si="10"/>
+        <v>-1.6165341015407364</v>
+      </c>
+      <c r="S29" s="21">
+        <f t="shared" si="11"/>
+        <v>-2.0558506264310452</v>
+      </c>
+      <c r="T29" s="21">
+        <f t="shared" si="12"/>
+        <v>-25.269999999999996</v>
+      </c>
+      <c r="U29" s="21" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="V29" s="22">
+        <f t="shared" si="14"/>
+        <v>-7.3537696819844527</v>
+      </c>
+      <c r="W29" s="14"/>
+      <c r="X29" s="14"/>
+      <c r="Y29" s="14"/>
+    </row>
+    <row r="30" spans="1:25" ht="12.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="23">
+        <v>44228</v>
+      </c>
+      <c r="B30" s="24">
+        <v>62.28</v>
+      </c>
+      <c r="C30" s="24">
+        <v>64.886513226256554</v>
+      </c>
+      <c r="D30" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="E30" s="25">
+        <v>59.619677885355706</v>
+      </c>
+      <c r="F30" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="G30" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="H30" s="24">
+        <v>58.208318489183632</v>
+      </c>
+      <c r="I30" s="25">
+        <v>57.225476240563857</v>
+      </c>
+      <c r="J30" s="25">
+        <v>39.04901835074115</v>
+      </c>
+      <c r="K30" s="25"/>
+      <c r="L30" s="26">
+        <v>50.644466838719538</v>
+      </c>
+      <c r="M30" s="25">
+        <f t="shared" si="0"/>
+        <v>2.6065132262565527</v>
+      </c>
+      <c r="N30" s="25" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="O30" s="25">
+        <f t="shared" si="2"/>
+        <v>-2.6603221146442948</v>
+      </c>
+      <c r="P30" s="25" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="Q30" s="26" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="R30" s="24">
+        <f t="shared" si="10"/>
+        <v>-4.0716815108163686</v>
+      </c>
+      <c r="S30" s="25">
+        <f t="shared" si="11"/>
+        <v>-5.0545237594361438</v>
+      </c>
+      <c r="T30" s="25">
+        <f t="shared" si="12"/>
+        <v>-23.230981649258851</v>
+      </c>
+      <c r="U30" s="25" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="V30" s="26">
+        <f t="shared" si="14"/>
+        <v>-11.635533161280463</v>
+      </c>
+      <c r="W30" s="34"/>
+      <c r="X30" s="16"/>
+      <c r="Y30" s="14"/>
+    </row>
+    <row r="31" spans="1:25" ht="12.5" x14ac:dyDescent="0.35">
+      <c r="A31" s="19">
+        <v>44256</v>
+      </c>
+      <c r="B31" s="20">
+        <v>65.7</v>
+      </c>
+      <c r="C31" s="20">
+        <v>62.606314978778052</v>
+      </c>
+      <c r="D31" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E31" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="F31" s="21">
+        <v>57.533353754765265</v>
+      </c>
+      <c r="G31" s="22">
+        <v>59.468054531099</v>
+      </c>
+      <c r="H31" s="20">
+        <v>56.41306152296481</v>
+      </c>
+      <c r="I31" s="21">
+        <v>57.884440251670995</v>
+      </c>
+      <c r="J31" s="21">
+        <v>37.5</v>
+      </c>
+      <c r="K31" s="21"/>
+      <c r="L31" s="22">
+        <v>49.869383750126126</v>
+      </c>
+      <c r="M31" s="21">
+        <f t="shared" si="0"/>
+        <v>-3.0936850212219511</v>
+      </c>
+      <c r="N31" s="21" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="O31" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="P31" s="21">
+        <f t="shared" si="3"/>
+        <v>-8.1666462452347375</v>
+      </c>
+      <c r="Q31" s="22">
+        <f t="shared" si="4"/>
+        <v>-6.231945468901003</v>
+      </c>
+      <c r="R31" s="20">
+        <f t="shared" si="10"/>
+        <v>-9.2869384770351928</v>
+      </c>
+      <c r="S31" s="21">
+        <f t="shared" si="11"/>
+        <v>-7.815559748329008</v>
+      </c>
+      <c r="T31" s="21">
+        <f t="shared" si="12"/>
+        <v>-28.200000000000003</v>
+      </c>
+      <c r="U31" s="21" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="V31" s="22">
+        <f t="shared" si="14"/>
+        <v>-15.830616249873877</v>
+      </c>
+      <c r="W31" s="14"/>
+      <c r="X31" s="14"/>
+      <c r="Y31" s="14"/>
+    </row>
+    <row r="32" spans="1:25" ht="12.5" x14ac:dyDescent="0.35">
+      <c r="A32" s="23">
+        <v>44287</v>
+      </c>
+      <c r="B32" s="24">
+        <v>65.33</v>
+      </c>
+      <c r="C32" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D32" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="E32" s="25">
+        <v>57.759494158396919</v>
+      </c>
+      <c r="F32" s="25">
+        <v>53.441134161924928</v>
+      </c>
+      <c r="G32" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="H32" s="24">
+        <v>57.154815961110053</v>
+      </c>
+      <c r="I32" s="25">
+        <v>57.131682346568333</v>
+      </c>
+      <c r="J32" s="25">
+        <v>54.549367669838865</v>
+      </c>
+      <c r="K32" s="25"/>
+      <c r="L32" s="26">
+        <v>51.370069434662739</v>
+      </c>
+      <c r="M32" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N32" s="25" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="O32" s="25">
+        <f t="shared" si="2"/>
+        <v>-7.5705058416030795</v>
+      </c>
+      <c r="P32" s="25">
+        <f t="shared" si="3"/>
+        <v>-11.88886583807507</v>
+      </c>
+      <c r="Q32" s="26" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="R32" s="24">
+        <f t="shared" si="10"/>
+        <v>-8.1751840388899453</v>
+      </c>
+      <c r="S32" s="25">
+        <f t="shared" si="11"/>
+        <v>-8.1983176534316655</v>
+      </c>
+      <c r="T32" s="25">
+        <f t="shared" si="12"/>
+        <v>-10.780632330161133</v>
+      </c>
+      <c r="U32" s="25" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="V32" s="26">
+        <f t="shared" si="14"/>
+        <v>-13.95993056533726</v>
+      </c>
+      <c r="W32" s="34"/>
+      <c r="X32" s="16"/>
+      <c r="Y32" s="14"/>
+    </row>
+    <row r="33" spans="1:26" ht="12.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="19">
+        <v>44317</v>
+      </c>
+      <c r="B33" s="20">
+        <v>68.31</v>
+      </c>
+      <c r="C33" s="20">
+        <v>69.288722684062876</v>
+      </c>
+      <c r="D33" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E33" s="21">
+        <v>62.23798897092756</v>
+      </c>
+      <c r="F33" s="21">
+        <v>55.900486056381872</v>
+      </c>
+      <c r="G33" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="H33" s="20">
+        <v>57.476386630282569</v>
+      </c>
+      <c r="I33" s="21">
+        <v>57.325744852794259</v>
+      </c>
+      <c r="J33" s="21">
+        <v>49.520660622241721</v>
+      </c>
+      <c r="K33" s="21">
+        <v>49.328048974399749</v>
+      </c>
+      <c r="L33" s="22">
+        <v>52.41015381484862</v>
+      </c>
+      <c r="M33" s="21">
+        <f t="shared" si="0"/>
+        <v>0.97872268406287333</v>
+      </c>
+      <c r="N33" s="21" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="O33" s="21">
+        <f t="shared" si="2"/>
+        <v>-6.0720110290724421</v>
+      </c>
+      <c r="P33" s="21">
+        <f t="shared" si="3"/>
+        <v>-12.40951394361813</v>
+      </c>
+      <c r="Q33" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="R33" s="20">
+        <f t="shared" si="10"/>
+        <v>-10.833613369717433</v>
+      </c>
+      <c r="S33" s="21">
+        <f t="shared" si="11"/>
+        <v>-10.984255147205744</v>
+      </c>
+      <c r="T33" s="21">
+        <f t="shared" si="12"/>
+        <v>-18.789339377758282</v>
+      </c>
+      <c r="U33" s="21">
+        <f t="shared" si="13"/>
+        <v>-18.981951025600253</v>
+      </c>
+      <c r="V33" s="22">
+        <f t="shared" si="14"/>
+        <v>-15.899846185151382</v>
+      </c>
+      <c r="W33" s="14"/>
+      <c r="X33" s="14"/>
+      <c r="Y33" s="14"/>
+    </row>
+    <row r="34" spans="1:26" ht="12.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="23">
+        <v>44348</v>
+      </c>
+      <c r="B34" s="24">
+        <v>73.41</v>
+      </c>
+      <c r="C34" s="24">
+        <v>71.79626346595731</v>
+      </c>
+      <c r="D34" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="E34" s="25">
+        <v>70.74043895845</v>
+      </c>
+      <c r="F34" s="25">
+        <v>65.216079716470702</v>
+      </c>
+      <c r="G34" s="26">
+        <v>64.524755170720113</v>
+      </c>
+      <c r="H34" s="24">
+        <v>60.337861205136583</v>
+      </c>
+      <c r="I34" s="25">
+        <v>60.609498072491327</v>
+      </c>
+      <c r="J34" s="25">
+        <v>48.733271945322819</v>
+      </c>
+      <c r="K34" s="25"/>
+      <c r="L34" s="26">
+        <v>53.265564910650347</v>
+      </c>
+      <c r="M34" s="25">
+        <f t="shared" si="0"/>
+        <v>-1.6137365340426868</v>
+      </c>
+      <c r="N34" s="25" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="O34" s="25">
+        <f t="shared" si="2"/>
+        <v>-2.6695610415499971</v>
+      </c>
+      <c r="P34" s="25">
+        <f t="shared" si="3"/>
+        <v>-8.1939202835292946</v>
+      </c>
+      <c r="Q34" s="26">
+        <f t="shared" si="4"/>
+        <v>-8.885244829279884</v>
+      </c>
+      <c r="R34" s="24">
+        <f t="shared" si="10"/>
+        <v>-13.072138794863413</v>
+      </c>
+      <c r="S34" s="25">
+        <f t="shared" si="11"/>
+        <v>-12.80050192750867</v>
+      </c>
+      <c r="T34" s="25">
+        <f t="shared" si="12"/>
+        <v>-24.676728054677177</v>
+      </c>
+      <c r="U34" s="25" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="V34" s="26">
+        <f t="shared" si="14"/>
+        <v>-20.144435089349649</v>
+      </c>
+      <c r="W34" s="34"/>
+      <c r="X34" s="16"/>
+      <c r="Y34" s="14"/>
+    </row>
+    <row r="35" spans="1:26" ht="12.5" x14ac:dyDescent="0.35">
+      <c r="W35" s="14"/>
+      <c r="X35" s="14"/>
+      <c r="Y35" s="14"/>
+      <c r="Z35" s="15"/>
+    </row>
+    <row r="36" spans="1:26" ht="12.5" x14ac:dyDescent="0.35">
+      <c r="A36" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="W36" s="14"/>
+      <c r="X36" s="14"/>
+      <c r="Y36" s="14"/>
+      <c r="Z36" s="15"/>
+    </row>
+    <row r="37" spans="1:26" ht="12.5" x14ac:dyDescent="0.35">
+      <c r="W37" s="14"/>
+      <c r="X37" s="14"/>
+      <c r="Y37" s="14"/>
+      <c r="Z37" s="15"/>
+    </row>
+    <row r="38" spans="1:26" ht="12.5" x14ac:dyDescent="0.35">
+      <c r="W38" s="14"/>
+      <c r="X38" s="14"/>
+      <c r="Y38" s="14"/>
+      <c r="Z38" s="15"/>
+    </row>
+    <row r="39" spans="1:26" ht="12.5" x14ac:dyDescent="0.35">
+      <c r="W39" s="14"/>
+      <c r="X39" s="14"/>
+      <c r="Y39" s="14"/>
+      <c r="Z39" s="15"/>
+    </row>
+    <row r="40" spans="1:26" ht="12.5" x14ac:dyDescent="0.35">
+      <c r="W40" s="14"/>
+      <c r="X40" s="14"/>
+      <c r="Y40" s="14"/>
+      <c r="Z40" s="15"/>
+    </row>
+    <row r="41" spans="1:26" ht="12.5" x14ac:dyDescent="0.35">
+      <c r="W41" s="14"/>
+      <c r="X41" s="14"/>
+      <c r="Y41" s="14"/>
+      <c r="Z41" s="15"/>
+    </row>
+    <row r="42" spans="1:26" ht="12.5" x14ac:dyDescent="0.35">
+      <c r="W42" s="14"/>
+      <c r="X42" s="14"/>
+      <c r="Y42" s="14"/>
+      <c r="Z42" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2012,15 +3530,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.6640625" customWidth="1"/>
-    <col min="3" max="3" width="34.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.07421875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.69140625" customWidth="1"/>
+    <col min="3" max="3" width="34.3046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="1:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="16" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="1:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2031,7 +3549,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="16" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
@@ -2042,7 +3560,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>12</v>
       </c>
@@ -2053,7 +3571,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
         <v>14</v>
       </c>
@@ -2064,7 +3582,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
         <v>17</v>
       </c>
@@ -2075,7 +3593,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>18</v>
       </c>
@@ -2086,7 +3604,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
         <v>1</v>
       </c>
@@ -2097,7 +3615,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="10" t="s">
         <v>5</v>
       </c>
@@ -2108,7 +3626,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="10" t="s">
         <v>23</v>
       </c>
@@ -2119,7 +3637,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="11" t="s">
         <v>26</v>
       </c>
@@ -2130,7 +3648,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:3" ht="16" thickTop="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
